--- a/esyluban/examples/dev/DataTables/test/define_from_excel_one.xlsx
+++ b/esyluban/examples/dev/DataTables/test/define_from_excel_one.xlsx
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.12380952380952" defaultRowHeight="15"/>
   <cols>
     <col width="13.752380952381" customWidth="1" style="2" min="1" max="1"/>
@@ -1134,6 +1134,16 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>e2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DemoE2</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>y1</t>
@@ -1154,6 +1164,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>icons</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>list,string</t>
@@ -1172,11 +1187,12 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A7:A8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
